--- a/从零开始学Slots/从零开始学Slots-20-数值篇-WaySlots(3).xlsx
+++ b/从零开始学Slots/从零开始学Slots-20-数值篇-WaySlots(3).xlsx
@@ -6443,6 +6443,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:L148" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -7419,5 +7422,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:Q77" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-20-数值篇-WaySlots(3).xlsx
+++ b/从零开始学Slots/从零开始学Slots-20-数值篇-WaySlots(3).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="186">
   <si>
     <r>
       <rPr>
@@ -5445,7 +5445,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5576,6 +5576,14 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -6490,11 +6498,11 @@
       <c r="A4" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>102</v>
+      <c r="B4" s="33">
+        <v>24</v>
+      </c>
+      <c r="C4" s="33">
+        <v>28</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>103</v>
@@ -7090,8 +7098,8 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21" t="s">
-        <v>143</v>
+      <c r="A32" s="34">
+        <v>12</v>
       </c>
       <c r="F32" s="19" t="n">
         <f aca="false">SUM(F20:F31)</f>
@@ -7254,11 +7262,11 @@
       <c r="A46" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="B46" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>165</v>
+      <c r="B46" s="33">
+        <v>24</v>
+      </c>
+      <c r="C46" s="33">
+        <v>28</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>166</v>

--- a/从零开始学Slots/从零开始学Slots-20-数值篇-WaySlots(3).xlsx
+++ b/从零开始学Slots/从零开始学Slots-20-数值篇-WaySlots(3).xlsx
@@ -5264,11 +5264,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -5445,7 +5446,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5583,6 +5584,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" applyNumberFormat="1" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7211,7 +7216,7 @@
       <c r="A41" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B41" s="25" t="n">
+      <c r="B41" s="35" t="n">
         <f aca="false">B39/B40</f>
         <v>0.31146240234375</v>
       </c>
